--- a/data/trans_orig/Q5414-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2007</t>
+          <t>Población según si es capaz de comer solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39231</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69793</t>
+          <t>69961</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61478</t>
+          <t>60638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90661</t>
+          <t>89049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>154600</t>
+          <t>155477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163536</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49135</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>68315</t>
+          <t>67347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123221</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>857</t>
+          <t>892</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28490</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>40355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>58061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>67712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,92%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45391</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>68329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>115580</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117506</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99581</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108362</t>
+          <t>108100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>116221</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>211913</t>
+          <t>212013</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221294</t>
+          <t>221249</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105218</t>
+          <t>105049</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>143854</t>
+          <t>144451</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>152174</t>
+          <t>152187</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>252357</t>
+          <t>252937</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>263032</t>
+          <t>263121</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>484502</t>
+          <t>484991</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>497122</t>
+          <t>496990</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,49 +4622,49 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>663783</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>655807</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>669677</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>663783</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>655489</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>670437</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1160</t>
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1145491</t>
+          <t>1145012</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1164476</t>
+          <t>1164796</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2012</t>
+          <t>Población según si es capaz de comer solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44281</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44656</t>
+          <t>44002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>88924</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12910</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>17577</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66332</t>
+          <t>65841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77262</t>
+          <t>78069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88582</t>
+          <t>88372</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100749</t>
+          <t>100741</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159769</t>
+          <t>160661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176439</t>
+          <t>175985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47320</t>
+          <t>46986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54752</t>
+          <t>54737</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66031</t>
+          <t>65949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76669</t>
+          <t>76711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116741</t>
+          <t>116150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129715</t>
+          <t>129399</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5548</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58480</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>80621</t>
+          <t>79981</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>143113</t>
+          <t>142240</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9348</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26118</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41637</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48887</t>
+          <t>48888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72311</t>
+          <t>72119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80470</t>
+          <t>80464</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7604</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>60487</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69115</t>
+          <t>69109</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>109623</t>
+          <t>110566</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>119818</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>6400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8012,7 +8012,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98055</t>
+          <t>98741</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>111207</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>130062</t>
+          <t>129957</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139936</t>
+          <t>139970</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>234206</t>
+          <t>233997</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248882</t>
+          <t>248786</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7729</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>7572</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11611</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>13809</t>
+          <t>14016</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113934</t>
+          <t>113180</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150549</t>
+          <t>150505</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>162045</t>
+          <t>162080</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>268383</t>
+          <t>267145</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280848</t>
+          <t>280986</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6826</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>21512</t>
+          <t>22159</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30127</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>33545</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50579</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>527334</t>
+          <t>528178</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>547452</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>693928</t>
+          <t>694417</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>718352</t>
+          <t>718993</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1229100</t>
+          <t>1228696</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1260517</t>
+          <t>1260631</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2016</t>
+          <t>Población según si es capaz de comer solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>33022</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42761</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81274</t>
+          <t>81064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87505</t>
+          <t>87497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6798</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10615</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13143</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80536</t>
+          <t>81297</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103042</t>
+          <t>103108</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113865</t>
+          <t>113883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>187626</t>
+          <t>186680</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199293</t>
+          <t>199550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10540</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>10548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129705</t>
+          <t>131715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142204</t>
+          <t>142233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2278</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9065</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>60760</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83667</t>
+          <t>83128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>147220</t>
+          <t>146860</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155509</t>
+          <t>155520</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>6876</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>794</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8479</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43180</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84133</t>
+          <t>84503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91809</t>
+          <t>91818</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7228</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7568</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41691</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47619</t>
+          <t>47623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>57494</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66180</t>
+          <t>66112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101248</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112654</t>
+          <t>112715</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>8127</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16667</t>
+          <t>16224</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105770</t>
+          <t>105870</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>131370</t>
+          <t>130819</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>143990</t>
+          <t>144655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>241205</t>
+          <t>241225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>255451</t>
+          <t>255746</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>10114</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>134168</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>167124</t>
+          <t>168474</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>301668</t>
+          <t>300351</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>18940</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13496</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33994</t>
+          <t>33473</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20709</t>
+          <t>20157</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43453</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>575425</t>
+          <t>574837</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>586341</t>
+          <t>586254</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>733836</t>
+          <t>733540</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>757364</t>
+          <t>757465</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1315238</t>
+          <t>1315140</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1341109</t>
+          <t>1340787</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2023</t>
+          <t>Población según si es capaz de comer solo en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13941,7 +13941,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57193</t>
+          <t>56448</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62995</t>
+          <t>62994</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112974</t>
+          <t>112758</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14284,7 +14284,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -14327,7 +14327,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74218</t>
+          <t>74768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -14450,7 +14450,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118525</t>
+          <t>117469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125825</t>
+          <t>125811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195814</t>
+          <t>195893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205276</t>
+          <t>205432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>6033</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1604</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12260</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>71084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79000</t>
+          <t>79182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>85290</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>145711</t>
+          <t>146436</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>155017</t>
+          <t>154938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1203</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15196,7 +15196,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -15239,7 +15239,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>3273</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>354</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15324,7 +15324,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>71395</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98761</t>
+          <t>98767</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102805</t>
+          <t>102817</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15402,7 +15402,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172154</t>
+          <t>172582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177072</t>
+          <t>177094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15652,7 +15652,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2141</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7552</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9549</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30447</t>
+          <t>30701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>34337</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>51390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>57017</t>
+          <t>56812</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84130</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90382</t>
+          <t>90568</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,29%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>460</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2208</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -16151,7 +16151,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1762</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55074</t>
+          <t>55454</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59240</t>
+          <t>59443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56274</t>
+          <t>56276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>61694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113577</t>
+          <t>113366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120187</t>
+          <t>120065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7515</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>121855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>328660</t>
+          <t>328870</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>339082</t>
+          <t>339023</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>453773</t>
+          <t>454608</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>461920</t>
+          <t>462392</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,99%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>715</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>527</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17148,7 +17148,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>146117</t>
+          <t>146365</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>179679</t>
+          <t>179342</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>186116</t>
+          <t>186115</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>326298</t>
+          <t>325866</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>333039</t>
+          <t>333041</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,82 +17416,82 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>3392</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>12143</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10356</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>15602</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>7576</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>3518</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>10356</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>5848</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>16012</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>14647</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,39 +17529,39 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>23569</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>11771</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>34088</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
           <t>2,28%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>23569</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>11833</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>34013</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
@@ -17569,7 +17569,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21517</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>44729</t>
+          <t>43678</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>631943</t>
+          <t>632311</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>642708</t>
+          <t>642709</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>990125</t>
+          <t>990126</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1017981</t>
+          <t>1017881</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1628130</t>
+          <t>1628340</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1655366</t>
+          <t>1655615</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5414-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Provincia-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31564</t>
+          <t>31311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69961</t>
+          <t>69778</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8826</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8018</t>
+          <t>7914</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60638</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89049</t>
+          <t>89832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155477</t>
+          <t>155644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163533</t>
+          <t>163550</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>50345</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>67347</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123770</t>
+          <t>122610</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5833</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11405</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21762</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>28513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>32672</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40355</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58061</t>
+          <t>58012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67712</t>
+          <t>67696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100239</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>108100</t>
+          <t>108857</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116221</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,7 +3745,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>212013</t>
+          <t>212257</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>221249</t>
+          <t>221216</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7617</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>105049</t>
+          <t>105203</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>144451</t>
+          <t>143232</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>152187</t>
+          <t>152185</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>252937</t>
+          <t>253056</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>263121</t>
+          <t>263200</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>484991</t>
+          <t>486132</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>496990</t>
+          <t>497134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>654809</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>669677</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1145012</t>
+          <t>1145656</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1164796</t>
+          <t>1164511</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>42984</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88924</t>
+          <t>86825</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5604,7 +5604,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12083</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17577</t>
+          <t>16884</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>66080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78069</t>
+          <t>78097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88372</t>
+          <t>88239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100741</t>
+          <t>100098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160661</t>
+          <t>161716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175985</t>
+          <t>176122</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>46542</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54737</t>
+          <t>54732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65949</t>
+          <t>65551</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>76711</t>
+          <t>76692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116150</t>
+          <t>116198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129399</t>
+          <t>129398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6644,7 +6644,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -6667,7 +6667,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>59343</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79981</t>
+          <t>81527</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>142240</t>
+          <t>141338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>993</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26676</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41938</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48888</t>
+          <t>48909</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72119</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80464</t>
+          <t>80474</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -7579,7 +7579,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46450</t>
+          <t>46469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>60487</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69109</t>
+          <t>69108</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>110182</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>119818</t>
+          <t>119842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>988</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13746</t>
+          <t>12454</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>961</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16660</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>98741</t>
+          <t>99150</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111207</t>
+          <t>110378</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>129957</t>
+          <t>130011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>139970</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>233997</t>
+          <t>233047</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248786</t>
+          <t>248980</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>14016</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>113180</t>
+          <t>112866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>150505</t>
+          <t>150871</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>162080</t>
+          <t>162138</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>267145</t>
+          <t>267460</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>280986</t>
+          <t>280786</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>528178</t>
+          <t>527851</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>547452</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>694417</t>
+          <t>694184</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>718993</t>
+          <t>718532</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1228696</t>
+          <t>1231346</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1260631</t>
+          <t>1262104</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9503,7 +9503,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5874</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33022</t>
+          <t>33238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>43784</t>
+          <t>44260</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81064</t>
+          <t>80323</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>87497</t>
+          <t>87496</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5998</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81297</t>
+          <t>80804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103108</t>
+          <t>101607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113883</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186680</t>
+          <t>187091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199550</t>
+          <t>199780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>10050</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131715</t>
+          <t>131551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142233</t>
+          <t>142220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>775</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60760</t>
+          <t>60832</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>83128</t>
+          <t>84303</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>146860</t>
+          <t>147446</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>155520</t>
+          <t>155510</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11390,7 +11390,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6876</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>791</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>42884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -11513,7 +11513,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84503</t>
+          <t>84730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91818</t>
+          <t>91821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11733,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7502</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1792</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10279</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42143</t>
+          <t>41957</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47623</t>
+          <t>48446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>56818</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66112</t>
+          <t>66165</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>101574</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112715</t>
+          <t>112504</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6411</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -12267,7 +12267,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2866</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>105870</t>
+          <t>105130</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>130819</t>
+          <t>131115</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144655</t>
+          <t>144576</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>241225</t>
+          <t>240082</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>255746</t>
+          <t>255134</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12793,7 +12793,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>8889</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168474</t>
+          <t>166136</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,7 +12901,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>300351</t>
+          <t>301576</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>574837</t>
+          <t>574420</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>586254</t>
+          <t>586161</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>733540</t>
+          <t>733546</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>757465</t>
+          <t>757487</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1315140</t>
+          <t>1314051</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1340787</t>
+          <t>1341043</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>470</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>417</t>
+          <t>467</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13974,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61159</t>
+          <t>63336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>56448</t>
+          <t>60003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62994</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>117060</t>
+          <t>124291</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112758</t>
+          <t>120589</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118893</t>
+          <t>125764</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>894</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -14264,7 +14264,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>894</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -14317,7 +14317,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5941</t>
+          <t>6712</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -14342,7 +14342,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7719</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -14430,27 +14430,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>78812</t>
+          <t>86443</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74768</t>
+          <t>81661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122799</t>
+          <t>128645</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117469</t>
+          <t>123265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125811</t>
+          <t>132103</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>201610</t>
+          <t>215088</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>195893</t>
+          <t>209689</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>205432</t>
+          <t>219093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,7 +14660,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -14705,12 +14705,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2323</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>553</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1645</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,27 +14808,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7385</t>
+          <t>7433</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68148</t>
+          <t>67084</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71084</t>
+          <t>69572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>83059</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79182</t>
+          <t>77618</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85290</t>
+          <t>83636</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>151208</t>
+          <t>148417</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146436</t>
+          <t>143702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154938</t>
+          <t>152427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1652</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>644</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,7 +15264,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>768</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -15342,27 +15342,27 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73999</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>79887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>101221</t>
+          <t>108025</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>98767</t>
+          <t>105208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102817</t>
+          <t>109637</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>175219</t>
+          <t>190536</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172582</t>
+          <t>187247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>177094</t>
+          <t>192420</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>422</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -15617,12 +15617,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>422</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -15652,12 +15652,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>493</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9380</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>33220</t>
+          <t>34891</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30701</t>
+          <t>32219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34337</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,27 +15833,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>54744</t>
+          <t>56748</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51390</t>
+          <t>53224</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>56812</t>
+          <t>59015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -15868,32 +15868,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>87964</t>
+          <t>91639</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>84155</t>
+          <t>87519</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>94598</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94062</t>
+          <t>98045</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1512</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>460</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2709</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -16141,7 +16141,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>846</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -16151,12 +16151,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3328</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2398</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>57929</t>
+          <t>57873</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>55454</t>
+          <t>55407</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>59418</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>59360</t>
+          <t>61253</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56276</t>
+          <t>57856</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>61694</t>
+          <t>63723</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>117288</t>
+          <t>119126</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113366</t>
+          <t>115226</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120065</t>
+          <t>122109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>65258</t>
+          <t>67309</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125519</t>
+          <t>127532</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -16529,12 +16529,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,7 +16554,7 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -16579,7 +16579,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7515</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>336077</t>
+          <t>160767</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>328870</t>
+          <t>156867</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>339023</t>
+          <t>163419</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>459331</t>
+          <t>312109</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>454608</t>
+          <t>307760</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>462392</t>
+          <t>314773</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>339182</t>
+          <t>164769</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>462436</t>
+          <t>316111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17063,12 +17063,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,22 +17088,22 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>9744</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7856</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -17166,27 +17166,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>146922</t>
+          <t>162895</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>146365</t>
+          <t>160247</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -17201,27 +17201,27 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>184225</t>
+          <t>209514</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>179342</t>
+          <t>203022</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>186115</t>
+          <t>212166</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>331146</t>
+          <t>372410</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>325866</t>
+          <t>365420</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>333041</t>
+          <t>375422</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>147080</t>
+          <t>163554</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>376321</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>45972</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>638183</t>
+          <t>703994</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>632311</t>
+          <t>697248</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>642709</t>
+          <t>708509</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1002644</t>
+          <t>869621</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>990126</t>
+          <t>860507</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1017881</t>
+          <t>877457</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1640828</t>
+          <t>1573615</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1628340</t>
+          <t>1562182</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1655615</t>
+          <t>1582616</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
